--- a/data/alertasRefacciones.xlsx
+++ b/data/alertasRefacciones.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-12 22:16:28</t>
+          <t>2025-11-28 18:48:26</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-12 22:16:28</t>
+          <t>2025-11-28 18:48:26</t>
         </is>
       </c>
     </row>
